--- a/feature/add-sso-spec/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/feature/add-sso-spec/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T14:21:54+00:00</t>
+    <t>2026-07-06T14:41:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
